--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351691</v>
+        <v>129351705</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503550</v>
+        <v>503874</v>
       </c>
       <c r="R3" t="n">
-        <v>7024488</v>
+        <v>7024459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351708</v>
+        <v>129351691</v>
       </c>
       <c r="B4" t="n">
-        <v>92480</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503779</v>
+        <v>503550</v>
       </c>
       <c r="R4" t="n">
-        <v>7024427</v>
+        <v>7024488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351699</v>
+        <v>129351726</v>
       </c>
       <c r="B5" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503869</v>
+        <v>503801</v>
       </c>
       <c r="R5" t="n">
-        <v>7024446</v>
+        <v>7024461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351726</v>
+        <v>129351708</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>92494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503801</v>
+        <v>503779</v>
       </c>
       <c r="R6" t="n">
-        <v>7024461</v>
+        <v>7024427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351705</v>
+        <v>129351699</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>91540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,50 +1187,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503874</v>
+        <v>503869</v>
       </c>
       <c r="R7" t="n">
-        <v>7024459</v>
+        <v>7024446</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
         <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351717</v>
+        <v>129351721</v>
       </c>
       <c r="B12" t="n">
-        <v>78054</v>
+        <v>91536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503809</v>
+        <v>503885</v>
       </c>
       <c r="R12" t="n">
-        <v>7024430</v>
+        <v>7024432</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351721</v>
+        <v>129351717</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>78054</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503885</v>
+        <v>503809</v>
       </c>
       <c r="R13" t="n">
-        <v>7024432</v>
+        <v>7024430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B14" t="n">
-        <v>92480</v>
+        <v>91540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R14" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>92494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R15" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>129351698</v>
       </c>
       <c r="B17" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351689</v>
+        <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>88803</v>
+        <v>91837</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4412</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503560</v>
+        <v>503861</v>
       </c>
       <c r="R21" t="n">
-        <v>7024494</v>
+        <v>7024449</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351713</v>
+        <v>129351694</v>
       </c>
       <c r="B22" t="n">
-        <v>91827</v>
+        <v>83007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503861</v>
+        <v>503809</v>
       </c>
       <c r="R22" t="n">
-        <v>7024449</v>
+        <v>7024430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B23" t="n">
-        <v>83007</v>
+        <v>88804</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R23" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2833,7 +2833,7 @@
         <v>129351715</v>
       </c>
       <c r="B24" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129351700</v>
       </c>
       <c r="B25" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>91538</v>
+        <v>92257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R26" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B27" t="n">
-        <v>92242</v>
+        <v>91536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R27" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>129351710</v>
       </c>
       <c r="B29" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,12 +3335,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351719</v>
+        <v>129351703</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>92257</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503825</v>
+        <v>503850</v>
       </c>
       <c r="R30" t="n">
-        <v>7024437</v>
+        <v>7024438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351703</v>
+        <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>92242</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503850</v>
+        <v>503825</v>
       </c>
       <c r="R31" t="n">
-        <v>7024438</v>
+        <v>7024437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351707</v>
+        <v>129351711</v>
       </c>
       <c r="B32" t="n">
-        <v>92480</v>
+        <v>91992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503860</v>
+        <v>503762</v>
       </c>
       <c r="R32" t="n">
-        <v>7024455</v>
+        <v>7024433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B34" t="n">
-        <v>91997</v>
+        <v>92494</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R34" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3900,7 +3900,7 @@
         <v>129351697</v>
       </c>
       <c r="B35" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B36" t="n">
-        <v>96924</v>
+        <v>91992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R36" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B37" t="n">
-        <v>91997</v>
+        <v>96950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R37" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351708</v>
+        <v>129351699</v>
       </c>
       <c r="B6" t="n">
-        <v>92494</v>
+        <v>91540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503779</v>
+        <v>503869</v>
       </c>
       <c r="R6" t="n">
-        <v>7024427</v>
+        <v>7024446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,32 +1176,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351699</v>
+        <v>129351708</v>
       </c>
       <c r="B7" t="n">
-        <v>91540</v>
+        <v>92495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503869</v>
+        <v>503779</v>
       </c>
       <c r="R7" t="n">
-        <v>7024446</v>
+        <v>7024427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,32 +1273,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351692</v>
+        <v>129351690</v>
       </c>
       <c r="B8" t="n">
-        <v>83007</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503783</v>
+        <v>503573</v>
       </c>
       <c r="R8" t="n">
-        <v>7024426</v>
+        <v>7024465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351693</v>
+        <v>129351692</v>
       </c>
       <c r="B9" t="n">
         <v>83007</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503790</v>
+        <v>503783</v>
       </c>
       <c r="R9" t="n">
-        <v>7024473</v>
+        <v>7024426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351690</v>
+        <v>129351693</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>83007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503573</v>
+        <v>503790</v>
       </c>
       <c r="R10" t="n">
-        <v>7024465</v>
+        <v>7024473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351724</v>
+        <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503977</v>
+        <v>503885</v>
       </c>
       <c r="R11" t="n">
-        <v>7024481</v>
+        <v>7024432</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351721</v>
+        <v>129351724</v>
       </c>
       <c r="B12" t="n">
-        <v>91536</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503885</v>
+        <v>503977</v>
       </c>
       <c r="R12" t="n">
-        <v>7024432</v>
+        <v>7024481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>91540</v>
+        <v>92495</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R14" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>92494</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R15" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B24" t="n">
-        <v>91837</v>
+        <v>91540</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>91838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3027,7 +3027,7 @@
         <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351710</v>
+        <v>129351719</v>
       </c>
       <c r="B29" t="n">
-        <v>91992</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503868</v>
+        <v>503825</v>
       </c>
       <c r="R29" t="n">
-        <v>7024419</v>
+        <v>7024437</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351703</v>
+        <v>129351710</v>
       </c>
       <c r="B30" t="n">
-        <v>92257</v>
+        <v>91993</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503850</v>
+        <v>503868</v>
       </c>
       <c r="R30" t="n">
-        <v>7024438</v>
+        <v>7024419</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351719</v>
+        <v>129351703</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>92258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503825</v>
+        <v>503850</v>
       </c>
       <c r="R31" t="n">
-        <v>7024437</v>
+        <v>7024438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B32" t="n">
-        <v>91992</v>
+        <v>92495</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R32" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351695</v>
+        <v>129351711</v>
       </c>
       <c r="B33" t="n">
-        <v>83007</v>
+        <v>91993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503792</v>
+        <v>503762</v>
       </c>
       <c r="R33" t="n">
-        <v>7024449</v>
+        <v>7024433</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351707</v>
+        <v>129351697</v>
       </c>
       <c r="B34" t="n">
-        <v>92494</v>
+        <v>91504</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503860</v>
+        <v>503903</v>
       </c>
       <c r="R34" t="n">
-        <v>7024455</v>
+        <v>7024440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351697</v>
+        <v>129351695</v>
       </c>
       <c r="B35" t="n">
-        <v>91504</v>
+        <v>83007</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503903</v>
+        <v>503792</v>
       </c>
       <c r="R35" t="n">
-        <v>7024440</v>
+        <v>7024449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>91992</v>
+        <v>96951</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R36" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>96950</v>
+        <v>91993</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R37" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -873,44 +873,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351691</v>
+        <v>129351708</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>92495</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503550</v>
+        <v>503779</v>
       </c>
       <c r="R4" t="n">
-        <v>7024488</v>
+        <v>7024427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,22 +970,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351726</v>
+        <v>129351699</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503801</v>
+        <v>503869</v>
       </c>
       <c r="R5" t="n">
-        <v>7024461</v>
+        <v>7024446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,22 +1067,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351699</v>
+        <v>129351691</v>
       </c>
       <c r="B6" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503869</v>
+        <v>503550</v>
       </c>
       <c r="R6" t="n">
-        <v>7024446</v>
+        <v>7024488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,44 +1164,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351708</v>
+        <v>129351726</v>
       </c>
       <c r="B7" t="n">
-        <v>92495</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503779</v>
+        <v>503801</v>
       </c>
       <c r="R7" t="n">
-        <v>7024427</v>
+        <v>7024461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,44 +1261,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351690</v>
+        <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>83007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503573</v>
+        <v>503783</v>
       </c>
       <c r="R8" t="n">
-        <v>7024465</v>
+        <v>7024426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,19 +1358,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351692</v>
+        <v>129351693</v>
       </c>
       <c r="B9" t="n">
         <v>83007</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503783</v>
+        <v>503790</v>
       </c>
       <c r="R9" t="n">
-        <v>7024426</v>
+        <v>7024473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,44 +1455,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351693</v>
+        <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>83007</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503790</v>
+        <v>503573</v>
       </c>
       <c r="R10" t="n">
-        <v>7024473</v>
+        <v>7024465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,12 +1552,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1649,12 +1649,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1746,12 +1746,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1940,12 +1940,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2037,12 +2037,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2134,44 +2134,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R17" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2219,6 +2219,11 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2231,44 +2236,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B18" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R18" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2316,11 +2321,6 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2333,12 +2333,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2430,12 +2430,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2527,12 +2527,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2624,12 +2624,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2721,12 +2721,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2818,12 +2818,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2915,12 +2915,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3012,44 +3012,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B26" t="n">
-        <v>92258</v>
+        <v>91536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R26" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3109,44 +3109,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B27" t="n">
-        <v>91536</v>
+        <v>92258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R27" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,12 +3206,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3303,22 +3303,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351719</v>
+        <v>129351710</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>91993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503825</v>
+        <v>503868</v>
       </c>
       <c r="R29" t="n">
-        <v>7024437</v>
+        <v>7024419</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3400,44 +3400,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351710</v>
+        <v>129351703</v>
       </c>
       <c r="B30" t="n">
-        <v>91993</v>
+        <v>92258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503868</v>
+        <v>503850</v>
       </c>
       <c r="R30" t="n">
-        <v>7024419</v>
+        <v>7024438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3497,44 +3497,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351703</v>
+        <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>92258</v>
+        <v>98706</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503850</v>
+        <v>503825</v>
       </c>
       <c r="R31" t="n">
-        <v>7024438</v>
+        <v>7024437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3594,12 +3594,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3691,44 +3691,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351711</v>
+        <v>129351697</v>
       </c>
       <c r="B33" t="n">
-        <v>91993</v>
+        <v>91504</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503762</v>
+        <v>503903</v>
       </c>
       <c r="R33" t="n">
-        <v>7024433</v>
+        <v>7024440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3788,44 +3788,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351697</v>
+        <v>129351711</v>
       </c>
       <c r="B34" t="n">
-        <v>91504</v>
+        <v>91993</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503903</v>
+        <v>503762</v>
       </c>
       <c r="R34" t="n">
-        <v>7024440</v>
+        <v>7024433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,12 +3885,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3982,44 +3982,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B36" t="n">
-        <v>96951</v>
+        <v>91993</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R36" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4079,44 +4079,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B37" t="n">
-        <v>91993</v>
+        <v>96952</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R37" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4176,12 +4176,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351725</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351705</v>
+        <v>129351699</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>91543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,50 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503874</v>
+        <v>503869</v>
       </c>
       <c r="R3" t="n">
-        <v>7024459</v>
+        <v>7024446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351708</v>
+        <v>129351691</v>
       </c>
       <c r="B4" t="n">
-        <v>92495</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503779</v>
+        <v>503550</v>
       </c>
       <c r="R4" t="n">
-        <v>7024427</v>
+        <v>7024488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351699</v>
+        <v>129351726</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503869</v>
+        <v>503801</v>
       </c>
       <c r="R5" t="n">
-        <v>7024446</v>
+        <v>7024461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351691</v>
+        <v>129351708</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>92498</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503550</v>
+        <v>503779</v>
       </c>
       <c r="R6" t="n">
-        <v>7024488</v>
+        <v>7024427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351726</v>
+        <v>129351705</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,34 +1171,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503801</v>
+        <v>503874</v>
       </c>
       <c r="R7" t="n">
-        <v>7024461</v>
+        <v>7024459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,7 +1276,7 @@
         <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>129351693</v>
       </c>
       <c r="B9" t="n">
-        <v>83007</v>
+        <v>83011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351721</v>
+        <v>129351724</v>
       </c>
       <c r="B11" t="n">
-        <v>91536</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503885</v>
+        <v>503977</v>
       </c>
       <c r="R11" t="n">
-        <v>7024432</v>
+        <v>7024481</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351724</v>
+        <v>129351721</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>91539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503977</v>
+        <v>503885</v>
       </c>
       <c r="R12" t="n">
-        <v>7024481</v>
+        <v>7024432</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,7 +1761,7 @@
         <v>129351717</v>
       </c>
       <c r="B13" t="n">
-        <v>78054</v>
+        <v>78056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R17" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,11 +2217,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R18" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2319,6 +2314,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129351718</v>
       </c>
       <c r="B20" t="n">
-        <v>78054</v>
+        <v>78056</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B22" t="n">
-        <v>83007</v>
+        <v>88807</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R22" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B23" t="n">
-        <v>88804</v>
+        <v>83011</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R23" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2833,7 +2833,7 @@
         <v>129351700</v>
       </c>
       <c r="B24" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129351715</v>
       </c>
       <c r="B25" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129351723</v>
       </c>
       <c r="B26" t="n">
-        <v>91536</v>
+        <v>91539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>129351702</v>
       </c>
       <c r="B27" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351710</v>
+        <v>129351719</v>
       </c>
       <c r="B29" t="n">
-        <v>91993</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503868</v>
+        <v>503825</v>
       </c>
       <c r="R29" t="n">
-        <v>7024419</v>
+        <v>7024437</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3415,7 +3415,7 @@
         <v>129351703</v>
       </c>
       <c r="B30" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351719</v>
+        <v>129351710</v>
       </c>
       <c r="B31" t="n">
-        <v>98706</v>
+        <v>91996</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3520,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503825</v>
+        <v>503868</v>
       </c>
       <c r="R31" t="n">
-        <v>7024437</v>
+        <v>7024419</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351707</v>
+        <v>129351695</v>
       </c>
       <c r="B32" t="n">
-        <v>92495</v>
+        <v>83011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503860</v>
+        <v>503792</v>
       </c>
       <c r="R32" t="n">
-        <v>7024455</v>
+        <v>7024449</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351697</v>
+        <v>129351707</v>
       </c>
       <c r="B33" t="n">
-        <v>91504</v>
+        <v>92498</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503903</v>
+        <v>503860</v>
       </c>
       <c r="R33" t="n">
-        <v>7024440</v>
+        <v>7024455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351711</v>
+        <v>129351697</v>
       </c>
       <c r="B34" t="n">
-        <v>91993</v>
+        <v>91507</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503762</v>
+        <v>503903</v>
       </c>
       <c r="R34" t="n">
-        <v>7024433</v>
+        <v>7024440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351695</v>
+        <v>129351711</v>
       </c>
       <c r="B35" t="n">
-        <v>83007</v>
+        <v>91996</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503792</v>
+        <v>503762</v>
       </c>
       <c r="R35" t="n">
-        <v>7024449</v>
+        <v>7024433</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
         <v>129351712</v>
       </c>
       <c r="B36" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>129351696</v>
       </c>
       <c r="B37" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351699</v>
+        <v>129351691</v>
       </c>
       <c r="B3" t="n">
-        <v>91543</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503869</v>
+        <v>503550</v>
       </c>
       <c r="R3" t="n">
-        <v>7024446</v>
+        <v>7024488</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351691</v>
+        <v>129351726</v>
       </c>
       <c r="B4" t="n">
         <v>79043</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503550</v>
+        <v>503801</v>
       </c>
       <c r="R4" t="n">
-        <v>7024488</v>
+        <v>7024461</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351726</v>
+        <v>129351708</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>92498</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503801</v>
+        <v>503779</v>
       </c>
       <c r="R5" t="n">
-        <v>7024461</v>
+        <v>7024427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351708</v>
+        <v>129351699</v>
       </c>
       <c r="B6" t="n">
-        <v>92498</v>
+        <v>91543</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503779</v>
+        <v>503869</v>
       </c>
       <c r="R6" t="n">
-        <v>7024427</v>
+        <v>7024446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B14" t="n">
-        <v>92498</v>
+        <v>91543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R14" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B15" t="n">
-        <v>91543</v>
+        <v>92498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R15" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351725</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129351691</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129351726</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351708</v>
+        <v>129351699</v>
       </c>
       <c r="B5" t="n">
-        <v>92498</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503779</v>
+        <v>503869</v>
       </c>
       <c r="R5" t="n">
-        <v>7024427</v>
+        <v>7024446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351699</v>
+        <v>129351708</v>
       </c>
       <c r="B6" t="n">
-        <v>91543</v>
+        <v>92500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503869</v>
+        <v>503779</v>
       </c>
       <c r="R6" t="n">
-        <v>7024446</v>
+        <v>7024427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,32 +1273,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351692</v>
+        <v>129351690</v>
       </c>
       <c r="B8" t="n">
-        <v>83011</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503783</v>
+        <v>503573</v>
       </c>
       <c r="R8" t="n">
-        <v>7024426</v>
+        <v>7024465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351693</v>
+        <v>129351692</v>
       </c>
       <c r="B9" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503790</v>
+        <v>503783</v>
       </c>
       <c r="R9" t="n">
-        <v>7024473</v>
+        <v>7024426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351690</v>
+        <v>129351693</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>83012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503573</v>
+        <v>503790</v>
       </c>
       <c r="R10" t="n">
-        <v>7024465</v>
+        <v>7024473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,7 +1567,7 @@
         <v>129351724</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>129351721</v>
       </c>
       <c r="B12" t="n">
-        <v>91539</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>129351717</v>
       </c>
       <c r="B13" t="n">
-        <v>78056</v>
+        <v>78057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>91543</v>
+        <v>92500</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R14" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>92498</v>
+        <v>91545</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R15" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B17" t="n">
-        <v>91543</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R17" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,6 +2217,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2243,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>91545</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R18" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,11 +2319,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129351718</v>
       </c>
       <c r="B20" t="n">
-        <v>78056</v>
+        <v>78057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B22" t="n">
-        <v>88807</v>
+        <v>83012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R22" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B23" t="n">
-        <v>83011</v>
+        <v>88809</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R23" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2833,7 +2833,7 @@
         <v>129351700</v>
       </c>
       <c r="B24" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129351715</v>
       </c>
       <c r="B25" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>91539</v>
+        <v>92263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R26" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B27" t="n">
-        <v>92261</v>
+        <v>91541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R27" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351719</v>
+        <v>129351710</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>91998</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503825</v>
+        <v>503868</v>
       </c>
       <c r="R29" t="n">
-        <v>7024437</v>
+        <v>7024419</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351703</v>
+        <v>129351719</v>
       </c>
       <c r="B30" t="n">
-        <v>92261</v>
+        <v>98712</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503850</v>
+        <v>503825</v>
       </c>
       <c r="R30" t="n">
-        <v>7024438</v>
+        <v>7024437</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351710</v>
+        <v>129351703</v>
       </c>
       <c r="B31" t="n">
-        <v>91996</v>
+        <v>92263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503868</v>
+        <v>503850</v>
       </c>
       <c r="R31" t="n">
-        <v>7024419</v>
+        <v>7024438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3609,7 +3609,7 @@
         <v>129351695</v>
       </c>
       <c r="B32" t="n">
-        <v>83011</v>
+        <v>83012</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351707</v>
+        <v>129351697</v>
       </c>
       <c r="B33" t="n">
-        <v>92498</v>
+        <v>91509</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503860</v>
+        <v>503903</v>
       </c>
       <c r="R33" t="n">
-        <v>7024455</v>
+        <v>7024440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351697</v>
+        <v>129351711</v>
       </c>
       <c r="B34" t="n">
-        <v>91507</v>
+        <v>91998</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503903</v>
+        <v>503762</v>
       </c>
       <c r="R34" t="n">
-        <v>7024440</v>
+        <v>7024433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B35" t="n">
-        <v>91996</v>
+        <v>92500</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R35" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>91996</v>
+        <v>96958</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R36" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>96956</v>
+        <v>91998</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R37" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351691</v>
+        <v>129351699</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503550</v>
+        <v>503869</v>
       </c>
       <c r="R3" t="n">
-        <v>7024488</v>
+        <v>7024446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351726</v>
+        <v>129351708</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>92504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503801</v>
+        <v>503779</v>
       </c>
       <c r="R4" t="n">
-        <v>7024461</v>
+        <v>7024427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351699</v>
+        <v>129351726</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503869</v>
+        <v>503801</v>
       </c>
       <c r="R5" t="n">
-        <v>7024446</v>
+        <v>7024461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351708</v>
+        <v>129351691</v>
       </c>
       <c r="B6" t="n">
-        <v>92500</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503779</v>
+        <v>503550</v>
       </c>
       <c r="R6" t="n">
-        <v>7024427</v>
+        <v>7024488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,7 +1276,7 @@
         <v>129351690</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351724</v>
+        <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91545</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503977</v>
+        <v>503885</v>
       </c>
       <c r="R11" t="n">
-        <v>7024481</v>
+        <v>7024432</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351721</v>
+        <v>129351724</v>
       </c>
       <c r="B12" t="n">
-        <v>91541</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503885</v>
+        <v>503977</v>
       </c>
       <c r="R12" t="n">
-        <v>7024432</v>
+        <v>7024481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1858,7 @@
         <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R17" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,11 +2217,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R18" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2319,6 +2314,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B22" t="n">
-        <v>83012</v>
+        <v>88813</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R22" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B23" t="n">
-        <v>88809</v>
+        <v>83012</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R23" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B24" t="n">
-        <v>91545</v>
+        <v>91847</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B25" t="n">
-        <v>91843</v>
+        <v>91549</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B26" t="n">
-        <v>92263</v>
+        <v>91545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R26" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B27" t="n">
-        <v>91541</v>
+        <v>92267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R27" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351710</v>
+        <v>129351703</v>
       </c>
       <c r="B29" t="n">
-        <v>91998</v>
+        <v>92267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503868</v>
+        <v>503850</v>
       </c>
       <c r="R29" t="n">
-        <v>7024419</v>
+        <v>7024438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351719</v>
+        <v>129351710</v>
       </c>
       <c r="B30" t="n">
-        <v>98712</v>
+        <v>92002</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503825</v>
+        <v>503868</v>
       </c>
       <c r="R30" t="n">
-        <v>7024437</v>
+        <v>7024419</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351703</v>
+        <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>92263</v>
+        <v>98716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503850</v>
+        <v>503825</v>
       </c>
       <c r="R31" t="n">
-        <v>7024438</v>
+        <v>7024437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351695</v>
+        <v>129351697</v>
       </c>
       <c r="B32" t="n">
-        <v>83012</v>
+        <v>91513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503792</v>
+        <v>503903</v>
       </c>
       <c r="R32" t="n">
-        <v>7024449</v>
+        <v>7024440</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351697</v>
+        <v>129351695</v>
       </c>
       <c r="B33" t="n">
-        <v>91509</v>
+        <v>83012</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503903</v>
+        <v>503792</v>
       </c>
       <c r="R33" t="n">
-        <v>7024440</v>
+        <v>7024449</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3803,7 +3803,7 @@
         <v>129351711</v>
       </c>
       <c r="B34" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>129351707</v>
       </c>
       <c r="B35" t="n">
-        <v>92500</v>
+        <v>92504</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>96958</v>
+        <v>96962</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129351699</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129351708</v>
       </c>
       <c r="B4" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351726</v>
+        <v>129351691</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503801</v>
+        <v>503550</v>
       </c>
       <c r="R5" t="n">
-        <v>7024461</v>
+        <v>7024488</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351691</v>
+        <v>129351726</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503550</v>
+        <v>503801</v>
       </c>
       <c r="R6" t="n">
-        <v>7024488</v>
+        <v>7024461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,7 +1276,7 @@
         <v>129351690</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>91545</v>
+        <v>91546</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B14" t="n">
-        <v>92504</v>
+        <v>91550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R14" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>92505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R15" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>129351698</v>
       </c>
       <c r="B17" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351713</v>
+        <v>129351689</v>
       </c>
       <c r="B21" t="n">
-        <v>91847</v>
+        <v>88814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>4412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503861</v>
+        <v>503560</v>
       </c>
       <c r="R21" t="n">
-        <v>7024449</v>
+        <v>7024494</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351689</v>
+        <v>129351713</v>
       </c>
       <c r="B22" t="n">
-        <v>88813</v>
+        <v>91848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503560</v>
+        <v>503861</v>
       </c>
       <c r="R22" t="n">
-        <v>7024494</v>
+        <v>7024449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,7 +2833,7 @@
         <v>129351715</v>
       </c>
       <c r="B24" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129351700</v>
       </c>
       <c r="B25" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>91545</v>
+        <v>92268</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R26" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B27" t="n">
-        <v>92267</v>
+        <v>91546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R27" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351703</v>
+        <v>129351710</v>
       </c>
       <c r="B29" t="n">
-        <v>92267</v>
+        <v>92003</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503850</v>
+        <v>503868</v>
       </c>
       <c r="R29" t="n">
-        <v>7024438</v>
+        <v>7024419</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351710</v>
+        <v>129351703</v>
       </c>
       <c r="B30" t="n">
-        <v>92002</v>
+        <v>92268</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503868</v>
+        <v>503850</v>
       </c>
       <c r="R30" t="n">
-        <v>7024419</v>
+        <v>7024438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3512,7 +3512,7 @@
         <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351697</v>
+        <v>129351711</v>
       </c>
       <c r="B32" t="n">
-        <v>91513</v>
+        <v>92003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503903</v>
+        <v>503762</v>
       </c>
       <c r="R32" t="n">
-        <v>7024440</v>
+        <v>7024433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351695</v>
+        <v>129351707</v>
       </c>
       <c r="B33" t="n">
-        <v>83012</v>
+        <v>92505</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503792</v>
+        <v>503860</v>
       </c>
       <c r="R33" t="n">
-        <v>7024449</v>
+        <v>7024455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351711</v>
+        <v>129351697</v>
       </c>
       <c r="B34" t="n">
-        <v>92002</v>
+        <v>91514</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503762</v>
+        <v>503903</v>
       </c>
       <c r="R34" t="n">
-        <v>7024433</v>
+        <v>7024440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351707</v>
+        <v>129351695</v>
       </c>
       <c r="B35" t="n">
-        <v>92504</v>
+        <v>83012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503860</v>
+        <v>503792</v>
       </c>
       <c r="R35" t="n">
-        <v>7024455</v>
+        <v>7024449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B36" t="n">
-        <v>96962</v>
+        <v>92003</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R36" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B37" t="n">
-        <v>92002</v>
+        <v>96970</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R37" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -1273,32 +1273,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351690</v>
+        <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>83012</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503573</v>
+        <v>503783</v>
       </c>
       <c r="R8" t="n">
-        <v>7024465</v>
+        <v>7024426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351692</v>
+        <v>129351693</v>
       </c>
       <c r="B9" t="n">
         <v>83012</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503783</v>
+        <v>503790</v>
       </c>
       <c r="R9" t="n">
-        <v>7024426</v>
+        <v>7024473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351693</v>
+        <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>83012</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503790</v>
+        <v>503573</v>
       </c>
       <c r="R10" t="n">
-        <v>7024473</v>
+        <v>7024465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351721</v>
+        <v>129351717</v>
       </c>
       <c r="B11" t="n">
-        <v>91546</v>
+        <v>78057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503885</v>
+        <v>503809</v>
       </c>
       <c r="R11" t="n">
-        <v>7024432</v>
+        <v>7024430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351724</v>
+        <v>129351721</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>91546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503977</v>
+        <v>503885</v>
       </c>
       <c r="R12" t="n">
-        <v>7024481</v>
+        <v>7024432</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351717</v>
+        <v>129351724</v>
       </c>
       <c r="B13" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503809</v>
+        <v>503977</v>
       </c>
       <c r="R13" t="n">
-        <v>7024430</v>
+        <v>7024481</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B21" t="n">
-        <v>88814</v>
+        <v>83012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R21" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B23" t="n">
-        <v>83012</v>
+        <v>88814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R23" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B25" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B26" t="n">
-        <v>92268</v>
+        <v>91546</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R26" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B27" t="n">
-        <v>91546</v>
+        <v>92268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R27" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351710</v>
+        <v>129351703</v>
       </c>
       <c r="B29" t="n">
-        <v>92003</v>
+        <v>92268</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503868</v>
+        <v>503850</v>
       </c>
       <c r="R29" t="n">
-        <v>7024419</v>
+        <v>7024438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351703</v>
+        <v>129351710</v>
       </c>
       <c r="B30" t="n">
-        <v>92268</v>
+        <v>92003</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503850</v>
+        <v>503868</v>
       </c>
       <c r="R30" t="n">
-        <v>7024438</v>
+        <v>7024419</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B32" t="n">
-        <v>92003</v>
+        <v>92505</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R32" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351707</v>
+        <v>129351697</v>
       </c>
       <c r="B33" t="n">
-        <v>92505</v>
+        <v>91514</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503860</v>
+        <v>503903</v>
       </c>
       <c r="R33" t="n">
-        <v>7024455</v>
+        <v>7024440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351697</v>
+        <v>129351695</v>
       </c>
       <c r="B34" t="n">
-        <v>91514</v>
+        <v>83012</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503903</v>
+        <v>503792</v>
       </c>
       <c r="R34" t="n">
-        <v>7024440</v>
+        <v>7024449</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351695</v>
+        <v>129351711</v>
       </c>
       <c r="B35" t="n">
-        <v>83012</v>
+        <v>92003</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503792</v>
+        <v>503762</v>
       </c>
       <c r="R35" t="n">
-        <v>7024449</v>
+        <v>7024433</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351699</v>
+        <v>129351691</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503869</v>
+        <v>503550</v>
       </c>
       <c r="R3" t="n">
-        <v>7024446</v>
+        <v>7024488</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351708</v>
+        <v>129351726</v>
       </c>
       <c r="B4" t="n">
-        <v>92505</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503779</v>
+        <v>503801</v>
       </c>
       <c r="R4" t="n">
-        <v>7024427</v>
+        <v>7024461</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351691</v>
+        <v>129351705</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503550</v>
+        <v>503874</v>
       </c>
       <c r="R5" t="n">
-        <v>7024488</v>
+        <v>7024459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351726</v>
+        <v>129351699</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503801</v>
+        <v>503869</v>
       </c>
       <c r="R6" t="n">
-        <v>7024461</v>
+        <v>7024446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,61 +1176,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351705</v>
+        <v>129351708</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>92505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503874</v>
+        <v>503779</v>
       </c>
       <c r="R7" t="n">
-        <v>7024459</v>
+        <v>7024427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,32 +1273,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351692</v>
+        <v>129351690</v>
       </c>
       <c r="B8" t="n">
-        <v>83012</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503783</v>
+        <v>503573</v>
       </c>
       <c r="R8" t="n">
-        <v>7024426</v>
+        <v>7024465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351693</v>
+        <v>129351692</v>
       </c>
       <c r="B9" t="n">
         <v>83012</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503790</v>
+        <v>503783</v>
       </c>
       <c r="R9" t="n">
-        <v>7024473</v>
+        <v>7024426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351690</v>
+        <v>129351693</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>83012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503573</v>
+        <v>503790</v>
       </c>
       <c r="R10" t="n">
-        <v>7024465</v>
+        <v>7024473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B24" t="n">
-        <v>91550</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>91550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>92003</v>
+        <v>96970</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R36" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>96970</v>
+        <v>92003</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R37" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351691</v>
+        <v>129351726</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503550</v>
+        <v>503801</v>
       </c>
       <c r="R3" t="n">
-        <v>7024488</v>
+        <v>7024461</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351726</v>
+        <v>129351691</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503801</v>
+        <v>503550</v>
       </c>
       <c r="R4" t="n">
-        <v>7024461</v>
+        <v>7024488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351699</v>
+        <v>129351708</v>
       </c>
       <c r="B6" t="n">
-        <v>91550</v>
+        <v>92508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503869</v>
+        <v>503779</v>
       </c>
       <c r="R6" t="n">
-        <v>7024446</v>
+        <v>7024427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,32 +1176,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351708</v>
+        <v>129351699</v>
       </c>
       <c r="B7" t="n">
-        <v>92505</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503779</v>
+        <v>503869</v>
       </c>
       <c r="R7" t="n">
-        <v>7024427</v>
+        <v>7024446</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,32 +1273,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351690</v>
+        <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>83012</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503573</v>
+        <v>503783</v>
       </c>
       <c r="R8" t="n">
-        <v>7024465</v>
+        <v>7024426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351692</v>
+        <v>129351693</v>
       </c>
       <c r="B9" t="n">
         <v>83012</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503783</v>
+        <v>503790</v>
       </c>
       <c r="R9" t="n">
-        <v>7024426</v>
+        <v>7024473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351693</v>
+        <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>83012</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503790</v>
+        <v>503573</v>
       </c>
       <c r="R10" t="n">
-        <v>7024473</v>
+        <v>7024465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351717</v>
+        <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>78057</v>
+        <v>91549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503809</v>
+        <v>503885</v>
       </c>
       <c r="R11" t="n">
-        <v>7024430</v>
+        <v>7024432</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351721</v>
+        <v>129351724</v>
       </c>
       <c r="B12" t="n">
-        <v>91546</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503885</v>
+        <v>503977</v>
       </c>
       <c r="R12" t="n">
-        <v>7024432</v>
+        <v>7024481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351724</v>
+        <v>129351717</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503977</v>
+        <v>503809</v>
       </c>
       <c r="R13" t="n">
-        <v>7024481</v>
+        <v>7024430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>91550</v>
+        <v>92508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R14" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>92505</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R15" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>129351698</v>
       </c>
       <c r="B17" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351694</v>
+        <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>83012</v>
+        <v>91851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503809</v>
+        <v>503861</v>
       </c>
       <c r="R21" t="n">
-        <v>7024430</v>
+        <v>7024449</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351713</v>
+        <v>129351689</v>
       </c>
       <c r="B22" t="n">
-        <v>91848</v>
+        <v>88814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503861</v>
+        <v>503560</v>
       </c>
       <c r="R22" t="n">
-        <v>7024449</v>
+        <v>7024494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B23" t="n">
-        <v>88814</v>
+        <v>83012</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R23" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>91553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B25" t="n">
-        <v>91550</v>
+        <v>91851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>91546</v>
+        <v>92271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R26" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B27" t="n">
-        <v>92268</v>
+        <v>91549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R27" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>129351703</v>
       </c>
       <c r="B29" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129351710</v>
       </c>
       <c r="B30" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351707</v>
+        <v>129351711</v>
       </c>
       <c r="B32" t="n">
-        <v>92505</v>
+        <v>92006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503860</v>
+        <v>503762</v>
       </c>
       <c r="R32" t="n">
-        <v>7024455</v>
+        <v>7024433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
         <v>129351697</v>
       </c>
       <c r="B33" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351695</v>
+        <v>129351707</v>
       </c>
       <c r="B34" t="n">
-        <v>83012</v>
+        <v>92508</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503792</v>
+        <v>503860</v>
       </c>
       <c r="R34" t="n">
-        <v>7024449</v>
+        <v>7024455</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351711</v>
+        <v>129351695</v>
       </c>
       <c r="B35" t="n">
-        <v>92003</v>
+        <v>83012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503762</v>
+        <v>503792</v>
       </c>
       <c r="R35" t="n">
-        <v>7024433</v>
+        <v>7024449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B36" t="n">
-        <v>96970</v>
+        <v>92006</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R36" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B37" t="n">
-        <v>92003</v>
+        <v>96973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R37" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351726</v>
+        <v>129351708</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>92508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503801</v>
+        <v>503779</v>
       </c>
       <c r="R3" t="n">
-        <v>7024461</v>
+        <v>7024427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351705</v>
+        <v>129351699</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,50 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503874</v>
+        <v>503869</v>
       </c>
       <c r="R5" t="n">
-        <v>7024459</v>
+        <v>7024446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351708</v>
+        <v>129351726</v>
       </c>
       <c r="B6" t="n">
-        <v>92508</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503779</v>
+        <v>503801</v>
       </c>
       <c r="R6" t="n">
-        <v>7024427</v>
+        <v>7024461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351699</v>
+        <v>129351705</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,34 +1171,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503869</v>
+        <v>503874</v>
       </c>
       <c r="R7" t="n">
-        <v>7024446</v>
+        <v>7024459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351721</v>
+        <v>129351717</v>
       </c>
       <c r="B11" t="n">
-        <v>91549</v>
+        <v>78057</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503885</v>
+        <v>503809</v>
       </c>
       <c r="R11" t="n">
-        <v>7024432</v>
+        <v>7024430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351724</v>
+        <v>129351721</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503977</v>
+        <v>503885</v>
       </c>
       <c r="R12" t="n">
-        <v>7024481</v>
+        <v>7024432</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351717</v>
+        <v>129351724</v>
       </c>
       <c r="B13" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503809</v>
+        <v>503977</v>
       </c>
       <c r="R13" t="n">
-        <v>7024430</v>
+        <v>7024481</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B14" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R14" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>92508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R15" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351713</v>
+        <v>129351694</v>
       </c>
       <c r="B21" t="n">
-        <v>91851</v>
+        <v>83012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503861</v>
+        <v>503809</v>
       </c>
       <c r="R21" t="n">
-        <v>7024449</v>
+        <v>7024430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351689</v>
+        <v>129351713</v>
       </c>
       <c r="B22" t="n">
-        <v>88814</v>
+        <v>91851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503560</v>
+        <v>503861</v>
       </c>
       <c r="R22" t="n">
-        <v>7024494</v>
+        <v>7024449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B23" t="n">
-        <v>83012</v>
+        <v>88814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R23" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B24" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B25" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B26" t="n">
-        <v>92271</v>
+        <v>91549</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R26" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B27" t="n">
-        <v>91549</v>
+        <v>92271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R27" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351703</v>
+        <v>129351719</v>
       </c>
       <c r="B29" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503850</v>
+        <v>503825</v>
       </c>
       <c r="R29" t="n">
-        <v>7024438</v>
+        <v>7024437</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351719</v>
+        <v>129351703</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503825</v>
+        <v>503850</v>
       </c>
       <c r="R31" t="n">
-        <v>7024437</v>
+        <v>7024438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>92006</v>
+        <v>96973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R36" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>96973</v>
+        <v>92006</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R37" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351708</v>
+        <v>129351699</v>
       </c>
       <c r="B3" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503779</v>
+        <v>503869</v>
       </c>
       <c r="R3" t="n">
-        <v>7024427</v>
+        <v>7024446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351691</v>
+        <v>129351708</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>92508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503550</v>
+        <v>503779</v>
       </c>
       <c r="R4" t="n">
-        <v>7024488</v>
+        <v>7024427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351699</v>
+        <v>129351691</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503869</v>
+        <v>503550</v>
       </c>
       <c r="R5" t="n">
-        <v>7024446</v>
+        <v>7024488</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351717</v>
+        <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>78057</v>
+        <v>91549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503809</v>
+        <v>503885</v>
       </c>
       <c r="R11" t="n">
-        <v>7024430</v>
+        <v>7024432</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351721</v>
+        <v>129351724</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503885</v>
+        <v>503977</v>
       </c>
       <c r="R12" t="n">
-        <v>7024432</v>
+        <v>7024481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351724</v>
+        <v>129351717</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503977</v>
+        <v>503809</v>
       </c>
       <c r="R13" t="n">
-        <v>7024481</v>
+        <v>7024430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351694</v>
+        <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>83012</v>
+        <v>91851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503809</v>
+        <v>503861</v>
       </c>
       <c r="R21" t="n">
-        <v>7024430</v>
+        <v>7024449</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351713</v>
+        <v>129351694</v>
       </c>
       <c r="B22" t="n">
-        <v>91851</v>
+        <v>83012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503861</v>
+        <v>503809</v>
       </c>
       <c r="R22" t="n">
-        <v>7024449</v>
+        <v>7024430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>91549</v>
+        <v>92271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R26" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B27" t="n">
-        <v>92271</v>
+        <v>91549</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R27" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351719</v>
+        <v>129351703</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503825</v>
+        <v>503850</v>
       </c>
       <c r="R29" t="n">
-        <v>7024437</v>
+        <v>7024438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351703</v>
+        <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503850</v>
+        <v>503825</v>
       </c>
       <c r="R31" t="n">
-        <v>7024438</v>
+        <v>7024437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351697</v>
+        <v>129351707</v>
       </c>
       <c r="B33" t="n">
-        <v>91517</v>
+        <v>92508</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503903</v>
+        <v>503860</v>
       </c>
       <c r="R33" t="n">
-        <v>7024440</v>
+        <v>7024455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351707</v>
+        <v>129351697</v>
       </c>
       <c r="B34" t="n">
-        <v>92508</v>
+        <v>91517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503860</v>
+        <v>503903</v>
       </c>
       <c r="R34" t="n">
-        <v>7024455</v>
+        <v>7024440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351699</v>
+        <v>129351708</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>92508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503869</v>
+        <v>503779</v>
       </c>
       <c r="R3" t="n">
-        <v>7024446</v>
+        <v>7024427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351708</v>
+        <v>129351691</v>
       </c>
       <c r="B4" t="n">
-        <v>92508</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503779</v>
+        <v>503550</v>
       </c>
       <c r="R4" t="n">
-        <v>7024427</v>
+        <v>7024488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351691</v>
+        <v>129351699</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503550</v>
+        <v>503869</v>
       </c>
       <c r="R5" t="n">
-        <v>7024488</v>
+        <v>7024446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351724</v>
+        <v>129351717</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503977</v>
+        <v>503809</v>
       </c>
       <c r="R12" t="n">
-        <v>7024481</v>
+        <v>7024430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351717</v>
+        <v>129351724</v>
       </c>
       <c r="B13" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503809</v>
+        <v>503977</v>
       </c>
       <c r="R13" t="n">
-        <v>7024430</v>
+        <v>7024481</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>92508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R14" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R15" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R17" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,6 +2217,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2243,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R18" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,11 +2319,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B22" t="n">
-        <v>83012</v>
+        <v>88814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R22" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B23" t="n">
-        <v>88814</v>
+        <v>83012</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R23" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B32" t="n">
-        <v>92006</v>
+        <v>92508</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R32" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351707</v>
+        <v>129351695</v>
       </c>
       <c r="B33" t="n">
-        <v>92508</v>
+        <v>83012</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503860</v>
+        <v>503792</v>
       </c>
       <c r="R33" t="n">
-        <v>7024455</v>
+        <v>7024449</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351697</v>
+        <v>129351711</v>
       </c>
       <c r="B34" t="n">
-        <v>91517</v>
+        <v>92006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503903</v>
+        <v>503762</v>
       </c>
       <c r="R34" t="n">
-        <v>7024440</v>
+        <v>7024433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351695</v>
+        <v>129351697</v>
       </c>
       <c r="B35" t="n">
-        <v>83012</v>
+        <v>91517</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503792</v>
+        <v>503903</v>
       </c>
       <c r="R35" t="n">
-        <v>7024449</v>
+        <v>7024440</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B36" t="n">
-        <v>96973</v>
+        <v>92006</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R36" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B37" t="n">
-        <v>92006</v>
+        <v>96973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R37" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351691</v>
+        <v>129351699</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503550</v>
+        <v>503869</v>
       </c>
       <c r="R4" t="n">
-        <v>7024488</v>
+        <v>7024446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351699</v>
+        <v>129351705</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503869</v>
+        <v>503874</v>
       </c>
       <c r="R5" t="n">
-        <v>7024446</v>
+        <v>7024459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351726</v>
+        <v>129351691</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1098,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503801</v>
+        <v>503550</v>
       </c>
       <c r="R6" t="n">
-        <v>7024461</v>
+        <v>7024488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351705</v>
+        <v>129351726</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,50 +1187,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503874</v>
+        <v>503801</v>
       </c>
       <c r="R7" t="n">
-        <v>7024459</v>
+        <v>7024461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351717</v>
+        <v>129351724</v>
       </c>
       <c r="B12" t="n">
-        <v>78057</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503809</v>
+        <v>503977</v>
       </c>
       <c r="R12" t="n">
-        <v>7024430</v>
+        <v>7024481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351724</v>
+        <v>129351717</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>78057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503977</v>
+        <v>503809</v>
       </c>
       <c r="R13" t="n">
-        <v>7024481</v>
+        <v>7024430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B14" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R14" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>92508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R15" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351713</v>
+        <v>129351689</v>
       </c>
       <c r="B21" t="n">
-        <v>91851</v>
+        <v>88814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>4412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503861</v>
+        <v>503560</v>
       </c>
       <c r="R21" t="n">
-        <v>7024449</v>
+        <v>7024494</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351689</v>
+        <v>129351713</v>
       </c>
       <c r="B22" t="n">
-        <v>88814</v>
+        <v>91851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503560</v>
+        <v>503861</v>
       </c>
       <c r="R22" t="n">
-        <v>7024494</v>
+        <v>7024449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B26" t="n">
-        <v>92271</v>
+        <v>91549</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R26" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B27" t="n">
-        <v>91549</v>
+        <v>92271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R27" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351703</v>
+        <v>129351710</v>
       </c>
       <c r="B29" t="n">
-        <v>92271</v>
+        <v>92006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503850</v>
+        <v>503868</v>
       </c>
       <c r="R29" t="n">
-        <v>7024438</v>
+        <v>7024419</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351710</v>
+        <v>129351719</v>
       </c>
       <c r="B30" t="n">
-        <v>92006</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503868</v>
+        <v>503825</v>
       </c>
       <c r="R30" t="n">
-        <v>7024419</v>
+        <v>7024437</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351719</v>
+        <v>129351703</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503825</v>
+        <v>503850</v>
       </c>
       <c r="R31" t="n">
-        <v>7024437</v>
+        <v>7024438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351695</v>
+        <v>129351711</v>
       </c>
       <c r="B33" t="n">
-        <v>83012</v>
+        <v>92006</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503792</v>
+        <v>503762</v>
       </c>
       <c r="R33" t="n">
-        <v>7024449</v>
+        <v>7024433</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351711</v>
+        <v>129351697</v>
       </c>
       <c r="B34" t="n">
-        <v>92006</v>
+        <v>91517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503762</v>
+        <v>503903</v>
       </c>
       <c r="R34" t="n">
-        <v>7024433</v>
+        <v>7024440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351697</v>
+        <v>129351695</v>
       </c>
       <c r="B35" t="n">
-        <v>91517</v>
+        <v>83012</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503903</v>
+        <v>503792</v>
       </c>
       <c r="R35" t="n">
-        <v>7024440</v>
+        <v>7024449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>92006</v>
+        <v>96973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R36" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>96973</v>
+        <v>92006</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R37" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,45 +772,61 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351708</v>
+        <v>129351705</v>
       </c>
       <c r="B3" t="n">
-        <v>92508</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503779</v>
+        <v>503874</v>
       </c>
       <c r="R3" t="n">
-        <v>7024427</v>
+        <v>7024459</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351699</v>
+        <v>129351691</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503869</v>
+        <v>503550</v>
       </c>
       <c r="R4" t="n">
-        <v>7024446</v>
+        <v>7024488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351705</v>
+        <v>129351726</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,50 +993,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503874</v>
+        <v>503801</v>
       </c>
       <c r="R5" t="n">
-        <v>7024459</v>
+        <v>7024461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351691</v>
+        <v>129351708</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>92508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503550</v>
+        <v>503779</v>
       </c>
       <c r="R6" t="n">
-        <v>7024488</v>
+        <v>7024427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351726</v>
+        <v>129351699</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503801</v>
+        <v>503869</v>
       </c>
       <c r="R7" t="n">
-        <v>7024461</v>
+        <v>7024446</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,32 +1370,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351693</v>
+        <v>129351690</v>
       </c>
       <c r="B9" t="n">
-        <v>83012</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503790</v>
+        <v>503573</v>
       </c>
       <c r="R9" t="n">
-        <v>7024473</v>
+        <v>7024465</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351690</v>
+        <v>129351693</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>83012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503573</v>
+        <v>503790</v>
       </c>
       <c r="R10" t="n">
-        <v>7024465</v>
+        <v>7024473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B21" t="n">
-        <v>88814</v>
+        <v>83012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R21" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B23" t="n">
-        <v>83012</v>
+        <v>88814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R23" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B24" t="n">
-        <v>91851</v>
+        <v>91553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>91851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351719</v>
+        <v>129351703</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>92271</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503825</v>
+        <v>503850</v>
       </c>
       <c r="R30" t="n">
-        <v>7024437</v>
+        <v>7024438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351703</v>
+        <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>92271</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503850</v>
+        <v>503825</v>
       </c>
       <c r="R31" t="n">
-        <v>7024438</v>
+        <v>7024437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351707</v>
+        <v>129351711</v>
       </c>
       <c r="B32" t="n">
-        <v>92508</v>
+        <v>92006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503860</v>
+        <v>503762</v>
       </c>
       <c r="R32" t="n">
-        <v>7024455</v>
+        <v>7024433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B33" t="n">
-        <v>92006</v>
+        <v>92508</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R33" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351725</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351705</v>
+        <v>129351699</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>91581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,50 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503874</v>
+        <v>503869</v>
       </c>
       <c r="R3" t="n">
-        <v>7024459</v>
+        <v>7024446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351691</v>
+        <v>129351705</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,34 +880,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503550</v>
+        <v>503874</v>
       </c>
       <c r="R4" t="n">
-        <v>7024488</v>
+        <v>7024459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,7 +985,7 @@
         <v>129351726</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351708</v>
+        <v>129351691</v>
       </c>
       <c r="B6" t="n">
-        <v>92508</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503779</v>
+        <v>503550</v>
       </c>
       <c r="R6" t="n">
-        <v>7024427</v>
+        <v>7024488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,32 +1176,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351699</v>
+        <v>129351708</v>
       </c>
       <c r="B7" t="n">
-        <v>91553</v>
+        <v>92536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503869</v>
+        <v>503779</v>
       </c>
       <c r="R7" t="n">
-        <v>7024446</v>
+        <v>7024427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,7 +1276,7 @@
         <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,32 +1370,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351690</v>
+        <v>129351693</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>83039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503573</v>
+        <v>503790</v>
       </c>
       <c r="R9" t="n">
-        <v>7024465</v>
+        <v>7024473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351693</v>
+        <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>83012</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503790</v>
+        <v>503573</v>
       </c>
       <c r="R10" t="n">
-        <v>7024473</v>
+        <v>7024465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,7 +1567,7 @@
         <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351724</v>
+        <v>129351717</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>78083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503977</v>
+        <v>503809</v>
       </c>
       <c r="R12" t="n">
-        <v>7024481</v>
+        <v>7024430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351717</v>
+        <v>129351724</v>
       </c>
       <c r="B13" t="n">
-        <v>78057</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503809</v>
+        <v>503977</v>
       </c>
       <c r="R13" t="n">
-        <v>7024430</v>
+        <v>7024481</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,7 +1858,7 @@
         <v>129351701</v>
       </c>
       <c r="B14" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>129351706</v>
       </c>
       <c r="B15" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R17" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,11 +2217,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R18" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2319,6 +2314,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129351718</v>
       </c>
       <c r="B20" t="n">
-        <v>78057</v>
+        <v>78083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351694</v>
+        <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>83012</v>
+        <v>91879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503809</v>
+        <v>503861</v>
       </c>
       <c r="R21" t="n">
-        <v>7024430</v>
+        <v>7024449</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351713</v>
+        <v>129351694</v>
       </c>
       <c r="B22" t="n">
-        <v>91851</v>
+        <v>83039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503861</v>
+        <v>503809</v>
       </c>
       <c r="R22" t="n">
-        <v>7024449</v>
+        <v>7024430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2736,7 +2736,7 @@
         <v>129351689</v>
       </c>
       <c r="B23" t="n">
-        <v>88814</v>
+        <v>88842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129351700</v>
       </c>
       <c r="B24" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129351715</v>
       </c>
       <c r="B25" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>91549</v>
+        <v>92299</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R26" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B27" t="n">
-        <v>92271</v>
+        <v>91577</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R27" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>129351710</v>
       </c>
       <c r="B29" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129351703</v>
       </c>
       <c r="B30" t="n">
-        <v>92271</v>
+        <v>92299</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351711</v>
+        <v>129351697</v>
       </c>
       <c r="B32" t="n">
-        <v>92006</v>
+        <v>91545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503762</v>
+        <v>503903</v>
       </c>
       <c r="R32" t="n">
-        <v>7024433</v>
+        <v>7024440</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3706,7 +3706,7 @@
         <v>129351707</v>
       </c>
       <c r="B33" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351697</v>
+        <v>129351711</v>
       </c>
       <c r="B34" t="n">
-        <v>91517</v>
+        <v>92034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503903</v>
+        <v>503762</v>
       </c>
       <c r="R34" t="n">
-        <v>7024440</v>
+        <v>7024433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3900,7 +3900,7 @@
         <v>129351695</v>
       </c>
       <c r="B35" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>96973</v>
+        <v>97002</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -869,61 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351705</v>
+        <v>129351708</v>
       </c>
       <c r="B4" t="n">
-        <v>57890</v>
+        <v>92536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503874</v>
+        <v>503779</v>
       </c>
       <c r="R4" t="n">
-        <v>7024459</v>
+        <v>7024427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351726</v>
+        <v>129351705</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>57890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,34 +977,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503801</v>
+        <v>503874</v>
       </c>
       <c r="R5" t="n">
-        <v>7024461</v>
+        <v>7024459</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351691</v>
+        <v>129351726</v>
       </c>
       <c r="B6" t="n">
         <v>79070</v>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503550</v>
+        <v>503801</v>
       </c>
       <c r="R6" t="n">
-        <v>7024488</v>
+        <v>7024461</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,32 +1176,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351708</v>
+        <v>129351691</v>
       </c>
       <c r="B7" t="n">
-        <v>92536</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503779</v>
+        <v>503550</v>
       </c>
       <c r="R7" t="n">
-        <v>7024427</v>
+        <v>7024488</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351697</v>
+        <v>129351711</v>
       </c>
       <c r="B32" t="n">
-        <v>91545</v>
+        <v>92034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503903</v>
+        <v>503762</v>
       </c>
       <c r="R32" t="n">
-        <v>7024440</v>
+        <v>7024433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351707</v>
+        <v>129351695</v>
       </c>
       <c r="B33" t="n">
-        <v>92536</v>
+        <v>83039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503860</v>
+        <v>503792</v>
       </c>
       <c r="R33" t="n">
-        <v>7024455</v>
+        <v>7024449</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B34" t="n">
-        <v>92034</v>
+        <v>92536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R34" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351695</v>
+        <v>129351697</v>
       </c>
       <c r="B35" t="n">
-        <v>83039</v>
+        <v>91545</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503792</v>
+        <v>503903</v>
       </c>
       <c r="R35" t="n">
-        <v>7024449</v>
+        <v>7024440</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351725</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351699</v>
+        <v>129351708</v>
       </c>
       <c r="B3" t="n">
-        <v>91581</v>
+        <v>92542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503869</v>
+        <v>503779</v>
       </c>
       <c r="R3" t="n">
-        <v>7024446</v>
+        <v>7024427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351708</v>
+        <v>129351699</v>
       </c>
       <c r="B4" t="n">
-        <v>92536</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503779</v>
+        <v>503869</v>
       </c>
       <c r="R4" t="n">
-        <v>7024427</v>
+        <v>7024446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351705</v>
+        <v>129351691</v>
       </c>
       <c r="B5" t="n">
-        <v>57890</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,50 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503874</v>
+        <v>503550</v>
       </c>
       <c r="R5" t="n">
-        <v>7024459</v>
+        <v>7024488</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1082,7 +1066,7 @@
         <v>129351726</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351691</v>
+        <v>129351705</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,34 +1171,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503550</v>
+        <v>503874</v>
       </c>
       <c r="R7" t="n">
-        <v>7024488</v>
+        <v>7024459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,12 +1261,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
         <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>83039</v>
+        <v>83044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,12 +1358,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1373,7 +1373,7 @@
         <v>129351693</v>
       </c>
       <c r="B9" t="n">
-        <v>83039</v>
+        <v>83044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,12 +1455,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
         <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,12 +1552,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
         <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1649,22 +1649,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351717</v>
+        <v>129351724</v>
       </c>
       <c r="B12" t="n">
-        <v>78083</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503809</v>
+        <v>503977</v>
       </c>
       <c r="R12" t="n">
-        <v>7024430</v>
+        <v>7024481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,22 +1746,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351724</v>
+        <v>129351717</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>78088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503977</v>
+        <v>503809</v>
       </c>
       <c r="R13" t="n">
-        <v>7024481</v>
+        <v>7024430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,44 +1843,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>91581</v>
+        <v>92542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R14" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,44 +1940,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>92536</v>
+        <v>91587</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R15" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,12 +2037,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2134,44 +2134,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B17" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R17" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2219,6 +2219,11 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2231,44 +2236,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B18" t="n">
-        <v>98756</v>
+        <v>91587</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R18" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2316,11 +2321,6 @@
           <t>2025-10-02</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2333,12 +2333,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,12 +2430,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
         <v>129351718</v>
       </c>
       <c r="B20" t="n">
-        <v>78083</v>
+        <v>78088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2527,12 +2527,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2542,7 +2542,7 @@
         <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2624,22 +2624,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B22" t="n">
-        <v>83039</v>
+        <v>88848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R22" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,22 +2721,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B23" t="n">
-        <v>88842</v>
+        <v>83044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R23" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,22 +2818,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B24" t="n">
-        <v>91581</v>
+        <v>91885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2915,22 +2915,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B25" t="n">
-        <v>91879</v>
+        <v>91587</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3012,12 +3012,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3027,7 +3027,7 @@
         <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3109,12 +3109,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3124,7 +3124,7 @@
         <v>129351723</v>
       </c>
       <c r="B27" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3206,12 +3206,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3303,12 +3303,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
         <v>129351710</v>
       </c>
       <c r="B29" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,12 +3400,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
         <v>129351703</v>
       </c>
       <c r="B30" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3497,12 +3497,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3512,7 +3512,7 @@
         <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3594,12 +3594,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
         <v>129351711</v>
       </c>
       <c r="B32" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3691,12 +3691,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3706,7 +3706,7 @@
         <v>129351695</v>
       </c>
       <c r="B33" t="n">
-        <v>83039</v>
+        <v>83044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3788,12 +3788,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3803,7 +3803,7 @@
         <v>129351707</v>
       </c>
       <c r="B34" t="n">
-        <v>92536</v>
+        <v>92542</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,12 +3885,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3900,7 +3900,7 @@
         <v>129351697</v>
       </c>
       <c r="B35" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,12 +3982,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -3997,7 +3997,7 @@
         <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,12 +4079,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4094,7 +4094,7 @@
         <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4176,12 +4176,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351725</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129351708</v>
       </c>
       <c r="B3" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351699</v>
+        <v>129351691</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503869</v>
+        <v>503550</v>
       </c>
       <c r="R4" t="n">
-        <v>7024446</v>
+        <v>7024488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351691</v>
+        <v>129351726</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503550</v>
+        <v>503801</v>
       </c>
       <c r="R5" t="n">
-        <v>7024488</v>
+        <v>7024461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351726</v>
+        <v>129351699</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503801</v>
+        <v>503869</v>
       </c>
       <c r="R6" t="n">
-        <v>7024461</v>
+        <v>7024446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>129351705</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>129351693</v>
       </c>
       <c r="B9" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351724</v>
+        <v>129351717</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>78089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503977</v>
+        <v>503809</v>
       </c>
       <c r="R12" t="n">
-        <v>7024481</v>
+        <v>7024430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351717</v>
+        <v>129351724</v>
       </c>
       <c r="B13" t="n">
-        <v>78088</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503809</v>
+        <v>503977</v>
       </c>
       <c r="R13" t="n">
-        <v>7024430</v>
+        <v>7024481</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,7 +1858,7 @@
         <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R17" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,11 +2217,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R18" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2319,6 +2314,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129351718</v>
       </c>
       <c r="B20" t="n">
-        <v>78088</v>
+        <v>78089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B22" t="n">
-        <v>88848</v>
+        <v>83045</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R22" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B23" t="n">
-        <v>83044</v>
+        <v>88849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R23" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2833,7 +2833,7 @@
         <v>129351715</v>
       </c>
       <c r="B24" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129351700</v>
       </c>
       <c r="B25" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B26" t="n">
-        <v>92305</v>
+        <v>91584</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R26" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B27" t="n">
-        <v>91583</v>
+        <v>92306</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R27" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>129351710</v>
       </c>
       <c r="B29" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>129351703</v>
       </c>
       <c r="B30" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>129351719</v>
       </c>
       <c r="B31" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B32" t="n">
-        <v>92040</v>
+        <v>92543</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R32" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351695</v>
+        <v>129351697</v>
       </c>
       <c r="B33" t="n">
-        <v>83044</v>
+        <v>91552</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503792</v>
+        <v>503903</v>
       </c>
       <c r="R33" t="n">
-        <v>7024449</v>
+        <v>7024440</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351707</v>
+        <v>129351695</v>
       </c>
       <c r="B34" t="n">
-        <v>92542</v>
+        <v>83045</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503860</v>
+        <v>503792</v>
       </c>
       <c r="R34" t="n">
-        <v>7024455</v>
+        <v>7024449</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351697</v>
+        <v>129351711</v>
       </c>
       <c r="B35" t="n">
-        <v>91551</v>
+        <v>92041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503903</v>
+        <v>503762</v>
       </c>
       <c r="R35" t="n">
-        <v>7024440</v>
+        <v>7024433</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
         <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351721</v>
+        <v>129351717</v>
       </c>
       <c r="B11" t="n">
-        <v>91584</v>
+        <v>78089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503885</v>
+        <v>503809</v>
       </c>
       <c r="R11" t="n">
-        <v>7024432</v>
+        <v>7024430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351717</v>
+        <v>129351724</v>
       </c>
       <c r="B12" t="n">
-        <v>78089</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503809</v>
+        <v>503977</v>
       </c>
       <c r="R12" t="n">
-        <v>7024430</v>
+        <v>7024481</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351724</v>
+        <v>129351721</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>91584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503977</v>
+        <v>503885</v>
       </c>
       <c r="R13" t="n">
-        <v>7024481</v>
+        <v>7024432</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351695</v>
+        <v>129351711</v>
       </c>
       <c r="B34" t="n">
-        <v>83045</v>
+        <v>92041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503792</v>
+        <v>503762</v>
       </c>
       <c r="R34" t="n">
-        <v>7024449</v>
+        <v>7024433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351711</v>
+        <v>129351695</v>
       </c>
       <c r="B35" t="n">
-        <v>92041</v>
+        <v>83045</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503762</v>
+        <v>503792</v>
       </c>
       <c r="R35" t="n">
-        <v>7024433</v>
+        <v>7024449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129351725</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351708</v>
+        <v>129351691</v>
       </c>
       <c r="B3" t="n">
-        <v>92543</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503779</v>
+        <v>503550</v>
       </c>
       <c r="R3" t="n">
-        <v>7024427</v>
+        <v>7024488</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351691</v>
+        <v>129351726</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503550</v>
+        <v>503801</v>
       </c>
       <c r="R4" t="n">
-        <v>7024488</v>
+        <v>7024461</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351726</v>
+        <v>129351699</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503801</v>
+        <v>503869</v>
       </c>
       <c r="R5" t="n">
-        <v>7024461</v>
+        <v>7024446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351699</v>
+        <v>129351708</v>
       </c>
       <c r="B6" t="n">
-        <v>91588</v>
+        <v>92548</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503869</v>
+        <v>503779</v>
       </c>
       <c r="R6" t="n">
-        <v>7024446</v>
+        <v>7024427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1276,7 +1276,7 @@
         <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>129351693</v>
       </c>
       <c r="B9" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351717</v>
+        <v>129351721</v>
       </c>
       <c r="B11" t="n">
-        <v>78089</v>
+        <v>91589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503809</v>
+        <v>503885</v>
       </c>
       <c r="R11" t="n">
-        <v>7024430</v>
+        <v>7024432</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>129351724</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351721</v>
+        <v>129351717</v>
       </c>
       <c r="B13" t="n">
-        <v>91584</v>
+        <v>78094</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503885</v>
+        <v>503809</v>
       </c>
       <c r="R13" t="n">
-        <v>7024432</v>
+        <v>7024430</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B14" t="n">
-        <v>92543</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R14" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B15" t="n">
-        <v>91588</v>
+        <v>92548</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R15" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>129351709</v>
       </c>
       <c r="B16" t="n">
-        <v>92543</v>
+        <v>92548</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B17" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R17" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,6 +2217,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2243,32 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B18" t="n">
-        <v>98769</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R18" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,11 +2319,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2348,7 +2348,7 @@
         <v>129351714</v>
       </c>
       <c r="B19" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>129351718</v>
       </c>
       <c r="B20" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>129351713</v>
       </c>
       <c r="B21" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>129351694</v>
       </c>
       <c r="B22" t="n">
-        <v>83045</v>
+        <v>83050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>129351689</v>
       </c>
       <c r="B23" t="n">
-        <v>88849</v>
+        <v>88854</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>129351715</v>
       </c>
       <c r="B24" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>129351700</v>
       </c>
       <c r="B25" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>129351723</v>
       </c>
       <c r="B26" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>129351702</v>
       </c>
       <c r="B27" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>129351716</v>
       </c>
       <c r="B28" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351710</v>
+        <v>129351719</v>
       </c>
       <c r="B29" t="n">
-        <v>92041</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,21 +3326,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503868</v>
+        <v>503825</v>
       </c>
       <c r="R29" t="n">
-        <v>7024419</v>
+        <v>7024437</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,32 +3412,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351703</v>
+        <v>129351710</v>
       </c>
       <c r="B30" t="n">
-        <v>92306</v>
+        <v>92046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503850</v>
+        <v>503868</v>
       </c>
       <c r="R30" t="n">
-        <v>7024438</v>
+        <v>7024419</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351719</v>
+        <v>129351703</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>92311</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503825</v>
+        <v>503850</v>
       </c>
       <c r="R31" t="n">
-        <v>7024437</v>
+        <v>7024438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351707</v>
+        <v>129351697</v>
       </c>
       <c r="B32" t="n">
-        <v>92543</v>
+        <v>91557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503860</v>
+        <v>503903</v>
       </c>
       <c r="R32" t="n">
-        <v>7024455</v>
+        <v>7024440</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351697</v>
+        <v>129351707</v>
       </c>
       <c r="B33" t="n">
-        <v>91552</v>
+        <v>92548</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503903</v>
+        <v>503860</v>
       </c>
       <c r="R33" t="n">
-        <v>7024440</v>
+        <v>7024455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351711</v>
+        <v>129351695</v>
       </c>
       <c r="B34" t="n">
-        <v>92041</v>
+        <v>83050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503762</v>
+        <v>503792</v>
       </c>
       <c r="R34" t="n">
-        <v>7024433</v>
+        <v>7024449</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351695</v>
+        <v>129351711</v>
       </c>
       <c r="B35" t="n">
-        <v>83045</v>
+        <v>92046</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503792</v>
+        <v>503762</v>
       </c>
       <c r="R35" t="n">
-        <v>7024449</v>
+        <v>7024433</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3997,7 +3997,7 @@
         <v>129351696</v>
       </c>
       <c r="B36" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>129351712</v>
       </c>
       <c r="B37" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351691</v>
+        <v>129351708</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>92548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503550</v>
+        <v>503779</v>
       </c>
       <c r="R3" t="n">
-        <v>7024488</v>
+        <v>7024427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351726</v>
+        <v>129351691</v>
       </c>
       <c r="B4" t="n">
         <v>79081</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503801</v>
+        <v>503550</v>
       </c>
       <c r="R4" t="n">
-        <v>7024461</v>
+        <v>7024488</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351699</v>
+        <v>129351726</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503869</v>
+        <v>503801</v>
       </c>
       <c r="R5" t="n">
-        <v>7024446</v>
+        <v>7024461</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351708</v>
+        <v>129351699</v>
       </c>
       <c r="B6" t="n">
-        <v>92548</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503779</v>
+        <v>503869</v>
       </c>
       <c r="R6" t="n">
-        <v>7024427</v>
+        <v>7024446</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,32 +1273,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351692</v>
+        <v>129351690</v>
       </c>
       <c r="B8" t="n">
-        <v>83050</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503783</v>
+        <v>503573</v>
       </c>
       <c r="R8" t="n">
-        <v>7024426</v>
+        <v>7024465</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351693</v>
+        <v>129351692</v>
       </c>
       <c r="B9" t="n">
         <v>83050</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503790</v>
+        <v>503783</v>
       </c>
       <c r="R9" t="n">
-        <v>7024473</v>
+        <v>7024426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351690</v>
+        <v>129351693</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>83050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503573</v>
+        <v>503790</v>
       </c>
       <c r="R10" t="n">
-        <v>7024465</v>
+        <v>7024473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351721</v>
+        <v>129351724</v>
       </c>
       <c r="B11" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503885</v>
+        <v>503977</v>
       </c>
       <c r="R11" t="n">
-        <v>7024432</v>
+        <v>7024481</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351724</v>
+        <v>129351721</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503977</v>
+        <v>503885</v>
       </c>
       <c r="R12" t="n">
-        <v>7024481</v>
+        <v>7024432</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351720</v>
+        <v>129351698</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503889</v>
+        <v>503868</v>
       </c>
       <c r="R17" t="n">
-        <v>7024460</v>
+        <v>7024418</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2217,11 +2217,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2248,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351698</v>
+        <v>129351720</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2283,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503868</v>
+        <v>503889</v>
       </c>
       <c r="R18" t="n">
-        <v>7024418</v>
+        <v>7024460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2319,6 +2314,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,10 +2636,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351694</v>
+        <v>129351689</v>
       </c>
       <c r="B22" t="n">
-        <v>83050</v>
+        <v>88854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>4412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503809</v>
+        <v>503560</v>
       </c>
       <c r="R22" t="n">
-        <v>7024430</v>
+        <v>7024494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351689</v>
+        <v>129351694</v>
       </c>
       <c r="B23" t="n">
-        <v>88854</v>
+        <v>83050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4412</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503560</v>
+        <v>503809</v>
       </c>
       <c r="R23" t="n">
-        <v>7024494</v>
+        <v>7024430</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351715</v>
+        <v>129351700</v>
       </c>
       <c r="B24" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503859</v>
+        <v>503865</v>
       </c>
       <c r="R24" t="n">
         <v>7024439</v>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351700</v>
+        <v>129351715</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503865</v>
+        <v>503859</v>
       </c>
       <c r="R25" t="n">
         <v>7024439</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351719</v>
+        <v>129351703</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>92311</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503825</v>
+        <v>503850</v>
       </c>
       <c r="R29" t="n">
-        <v>7024437</v>
+        <v>7024438</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351710</v>
+        <v>129351719</v>
       </c>
       <c r="B30" t="n">
-        <v>92046</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503868</v>
+        <v>503825</v>
       </c>
       <c r="R30" t="n">
-        <v>7024419</v>
+        <v>7024437</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351703</v>
+        <v>129351710</v>
       </c>
       <c r="B31" t="n">
-        <v>92311</v>
+        <v>92046</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503850</v>
+        <v>503868</v>
       </c>
       <c r="R31" t="n">
-        <v>7024438</v>
+        <v>7024419</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351697</v>
+        <v>129351695</v>
       </c>
       <c r="B32" t="n">
-        <v>91557</v>
+        <v>83050</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503903</v>
+        <v>503792</v>
       </c>
       <c r="R32" t="n">
-        <v>7024440</v>
+        <v>7024449</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351707</v>
+        <v>129351711</v>
       </c>
       <c r="B33" t="n">
-        <v>92548</v>
+        <v>92046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503860</v>
+        <v>503762</v>
       </c>
       <c r="R33" t="n">
-        <v>7024455</v>
+        <v>7024433</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3800,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351695</v>
+        <v>129351707</v>
       </c>
       <c r="B34" t="n">
-        <v>83050</v>
+        <v>92548</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503792</v>
+        <v>503860</v>
       </c>
       <c r="R34" t="n">
-        <v>7024449</v>
+        <v>7024455</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351711</v>
+        <v>129351697</v>
       </c>
       <c r="B35" t="n">
-        <v>92046</v>
+        <v>91557</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503762</v>
+        <v>503903</v>
       </c>
       <c r="R35" t="n">
-        <v>7024433</v>
+        <v>7024440</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351691</v>
+        <v>129351705</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503550</v>
+        <v>503874</v>
       </c>
       <c r="R4" t="n">
-        <v>7024488</v>
+        <v>7024459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351726</v>
+        <v>129351699</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503801</v>
+        <v>503869</v>
       </c>
       <c r="R5" t="n">
-        <v>7024461</v>
+        <v>7024446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351699</v>
+        <v>129351691</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503869</v>
+        <v>503550</v>
       </c>
       <c r="R6" t="n">
-        <v>7024446</v>
+        <v>7024488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351705</v>
+        <v>129351726</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,50 +1187,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503874</v>
+        <v>503801</v>
       </c>
       <c r="R7" t="n">
-        <v>7024459</v>
+        <v>7024461</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,32 +1273,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351690</v>
+        <v>129351692</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>83050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503573</v>
+        <v>503783</v>
       </c>
       <c r="R8" t="n">
-        <v>7024465</v>
+        <v>7024426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351692</v>
+        <v>129351693</v>
       </c>
       <c r="B9" t="n">
         <v>83050</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503783</v>
+        <v>503790</v>
       </c>
       <c r="R9" t="n">
-        <v>7024426</v>
+        <v>7024473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1467,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351693</v>
+        <v>129351690</v>
       </c>
       <c r="B10" t="n">
-        <v>83050</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503790</v>
+        <v>503573</v>
       </c>
       <c r="R10" t="n">
-        <v>7024473</v>
+        <v>7024465</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1855,32 +1855,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351701</v>
+        <v>129351706</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>92548</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503861</v>
+        <v>503942</v>
       </c>
       <c r="R14" t="n">
-        <v>7024434</v>
+        <v>7024461</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,32 +1952,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351706</v>
+        <v>129351701</v>
       </c>
       <c r="B15" t="n">
-        <v>92548</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503942</v>
+        <v>503861</v>
       </c>
       <c r="R15" t="n">
-        <v>7024461</v>
+        <v>7024434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2539,10 +2539,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351713</v>
+        <v>129351694</v>
       </c>
       <c r="B21" t="n">
-        <v>91891</v>
+        <v>83050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2550,21 +2550,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503861</v>
+        <v>503809</v>
       </c>
       <c r="R21" t="n">
-        <v>7024449</v>
+        <v>7024430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2733,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351694</v>
+        <v>129351713</v>
       </c>
       <c r="B23" t="n">
-        <v>83050</v>
+        <v>91891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2744,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503809</v>
+        <v>503861</v>
       </c>
       <c r="R23" t="n">
-        <v>7024430</v>
+        <v>7024449</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,32 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351723</v>
+        <v>129351702</v>
       </c>
       <c r="B26" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503891</v>
+        <v>503861</v>
       </c>
       <c r="R26" t="n">
-        <v>7024440</v>
+        <v>7024434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3121,32 +3121,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351702</v>
+        <v>129351723</v>
       </c>
       <c r="B27" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503861</v>
+        <v>503891</v>
       </c>
       <c r="R27" t="n">
-        <v>7024434</v>
+        <v>7024440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3315,32 +3315,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351703</v>
+        <v>129351719</v>
       </c>
       <c r="B29" t="n">
-        <v>92311</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503850</v>
+        <v>503825</v>
       </c>
       <c r="R29" t="n">
-        <v>7024438</v>
+        <v>7024437</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351719</v>
+        <v>129351710</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>92046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503825</v>
+        <v>503868</v>
       </c>
       <c r="R30" t="n">
-        <v>7024437</v>
+        <v>7024419</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3509,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351710</v>
+        <v>129351703</v>
       </c>
       <c r="B31" t="n">
-        <v>92046</v>
+        <v>92311</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503868</v>
+        <v>503850</v>
       </c>
       <c r="R31" t="n">
-        <v>7024419</v>
+        <v>7024438</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,32 +3606,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351695</v>
+        <v>129351711</v>
       </c>
       <c r="B32" t="n">
-        <v>83050</v>
+        <v>92046</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503792</v>
+        <v>503762</v>
       </c>
       <c r="R32" t="n">
-        <v>7024449</v>
+        <v>7024433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351711</v>
+        <v>129351707</v>
       </c>
       <c r="B33" t="n">
-        <v>92046</v>
+        <v>92548</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503762</v>
+        <v>503860</v>
       </c>
       <c r="R33" t="n">
-        <v>7024433</v>
+        <v>7024455</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,10 +3800,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351707</v>
+        <v>129351697</v>
       </c>
       <c r="B34" t="n">
-        <v>92548</v>
+        <v>91557</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3811,21 +3811,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3835,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503860</v>
+        <v>503903</v>
       </c>
       <c r="R34" t="n">
-        <v>7024455</v>
+        <v>7024440</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3897,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351697</v>
+        <v>129351695</v>
       </c>
       <c r="B35" t="n">
-        <v>91557</v>
+        <v>83050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503903</v>
+        <v>503792</v>
       </c>
       <c r="R35" t="n">
-        <v>7024440</v>
+        <v>7024449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351696</v>
+        <v>129351712</v>
       </c>
       <c r="B36" t="n">
-        <v>97020</v>
+        <v>92046</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503909</v>
+        <v>503774</v>
       </c>
       <c r="R36" t="n">
-        <v>7024442</v>
+        <v>7024452</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,32 +4091,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351712</v>
+        <v>129351696</v>
       </c>
       <c r="B37" t="n">
-        <v>92046</v>
+        <v>97020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503774</v>
+        <v>503909</v>
       </c>
       <c r="R37" t="n">
-        <v>7024452</v>
+        <v>7024442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129351725</v>
+        <v>129351696</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503787</v>
+        <v>503909</v>
       </c>
       <c r="R2" t="n">
-        <v>7024434</v>
+        <v>7024442</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129351708</v>
+        <v>129351713</v>
       </c>
       <c r="B3" t="n">
-        <v>92548</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503779</v>
+        <v>503861</v>
       </c>
       <c r="R3" t="n">
-        <v>7024427</v>
+        <v>7024449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129351705</v>
+        <v>129351714</v>
       </c>
       <c r="B4" t="n">
-        <v>57896</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,50 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503874</v>
+        <v>503868</v>
       </c>
       <c r="R4" t="n">
-        <v>7024459</v>
+        <v>7024422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129351699</v>
+        <v>129351715</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503869</v>
+        <v>503859</v>
       </c>
       <c r="R5" t="n">
-        <v>7024446</v>
+        <v>7024439</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129351691</v>
+        <v>129351716</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503550</v>
+        <v>503759</v>
       </c>
       <c r="R6" t="n">
-        <v>7024488</v>
+        <v>7024433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129351726</v>
+        <v>129351721</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503801</v>
+        <v>503885</v>
       </c>
       <c r="R7" t="n">
-        <v>7024461</v>
+        <v>7024432</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129351692</v>
+        <v>129351723</v>
       </c>
       <c r="B8" t="n">
-        <v>83050</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503783</v>
+        <v>503891</v>
       </c>
       <c r="R8" t="n">
-        <v>7024426</v>
+        <v>7024440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129351693</v>
+        <v>129351698</v>
       </c>
       <c r="B9" t="n">
-        <v>83050</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503790</v>
+        <v>503868</v>
       </c>
       <c r="R9" t="n">
-        <v>7024473</v>
+        <v>7024418</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129351690</v>
+        <v>129351699</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503573</v>
+        <v>503869</v>
       </c>
       <c r="R10" t="n">
-        <v>7024465</v>
+        <v>7024446</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129351724</v>
+        <v>129351700</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>503977</v>
+        <v>503865</v>
       </c>
       <c r="R11" t="n">
-        <v>7024481</v>
+        <v>7024439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129351721</v>
+        <v>129351701</v>
       </c>
       <c r="B12" t="n">
-        <v>91589</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>503885</v>
+        <v>503861</v>
       </c>
       <c r="R12" t="n">
-        <v>7024432</v>
+        <v>7024434</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129351717</v>
+        <v>129351710</v>
       </c>
       <c r="B13" t="n">
-        <v>78094</v>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>503809</v>
+        <v>503868</v>
       </c>
       <c r="R13" t="n">
-        <v>7024430</v>
+        <v>7024419</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129351706</v>
+        <v>129351711</v>
       </c>
       <c r="B14" t="n">
-        <v>92548</v>
+        <v>92369</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>503942</v>
+        <v>503762</v>
       </c>
       <c r="R14" t="n">
-        <v>7024461</v>
+        <v>7024433</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129351701</v>
+        <v>129351712</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>503861</v>
+        <v>503774</v>
       </c>
       <c r="R15" t="n">
-        <v>7024434</v>
+        <v>7024452</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129351709</v>
+        <v>129351702</v>
       </c>
       <c r="B16" t="n">
-        <v>92548</v>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>503768</v>
+        <v>503861</v>
       </c>
       <c r="R16" t="n">
-        <v>7024431</v>
+        <v>7024434</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129351698</v>
+        <v>129351703</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>92632</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>503868</v>
+        <v>503850</v>
       </c>
       <c r="R17" t="n">
-        <v>7024418</v>
+        <v>7024438</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129351720</v>
+        <v>129351689</v>
       </c>
       <c r="B18" t="n">
-        <v>98774</v>
+        <v>89156</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>503889</v>
+        <v>503560</v>
       </c>
       <c r="R18" t="n">
-        <v>7024460</v>
+        <v>7024494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2314,11 +2298,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2345,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129351714</v>
+        <v>129351706</v>
       </c>
       <c r="B19" t="n">
-        <v>91891</v>
+        <v>92869</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2380,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>503868</v>
+        <v>503942</v>
       </c>
       <c r="R19" t="n">
-        <v>7024422</v>
+        <v>7024461</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129351718</v>
+        <v>129351707</v>
       </c>
       <c r="B20" t="n">
-        <v>78094</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2477,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>503792</v>
+        <v>503860</v>
       </c>
       <c r="R20" t="n">
-        <v>7024449</v>
+        <v>7024455</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2539,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129351694</v>
+        <v>129351708</v>
       </c>
       <c r="B21" t="n">
-        <v>83050</v>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2574,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>503809</v>
+        <v>503779</v>
       </c>
       <c r="R21" t="n">
-        <v>7024430</v>
+        <v>7024427</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129351689</v>
+        <v>129351709</v>
       </c>
       <c r="B22" t="n">
-        <v>88854</v>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2671,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>503560</v>
+        <v>503768</v>
       </c>
       <c r="R22" t="n">
-        <v>7024494</v>
+        <v>7024431</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2733,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129351713</v>
+        <v>129351697</v>
       </c>
       <c r="B23" t="n">
-        <v>91891</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2768,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>503861</v>
+        <v>503903</v>
       </c>
       <c r="R23" t="n">
-        <v>7024449</v>
+        <v>7024440</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129351700</v>
+        <v>129351691</v>
       </c>
       <c r="B24" t="n">
-        <v>91593</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2865,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503865</v>
+        <v>503550</v>
       </c>
       <c r="R24" t="n">
-        <v>7024439</v>
+        <v>7024488</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2927,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129351715</v>
+        <v>129351724</v>
       </c>
       <c r="B25" t="n">
-        <v>91891</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2962,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503859</v>
+        <v>503977</v>
       </c>
       <c r="R25" t="n">
-        <v>7024439</v>
+        <v>7024481</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3024,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129351702</v>
+        <v>129351725</v>
       </c>
       <c r="B26" t="n">
-        <v>92311</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3059,7 +3038,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503861</v>
+        <v>503787</v>
       </c>
       <c r="R26" t="n">
         <v>7024434</v>
@@ -3121,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129351723</v>
+        <v>129351726</v>
       </c>
       <c r="B27" t="n">
-        <v>91589</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3156,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503891</v>
+        <v>503801</v>
       </c>
       <c r="R27" t="n">
-        <v>7024440</v>
+        <v>7024461</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3218,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129351716</v>
+        <v>129351692</v>
       </c>
       <c r="B28" t="n">
-        <v>91891</v>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3229,21 +3208,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3253,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503759</v>
+        <v>503783</v>
       </c>
       <c r="R28" t="n">
-        <v>7024433</v>
+        <v>7024426</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3315,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129351719</v>
+        <v>129351693</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3350,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503825</v>
+        <v>503790</v>
       </c>
       <c r="R29" t="n">
-        <v>7024437</v>
+        <v>7024473</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3412,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129351710</v>
+        <v>129351694</v>
       </c>
       <c r="B30" t="n">
-        <v>92046</v>
+        <v>83307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503868</v>
+        <v>503809</v>
       </c>
       <c r="R30" t="n">
-        <v>7024419</v>
+        <v>7024430</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129351703</v>
+        <v>129351695</v>
       </c>
       <c r="B31" t="n">
-        <v>92311</v>
+        <v>83307</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3544,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503850</v>
+        <v>503792</v>
       </c>
       <c r="R31" t="n">
-        <v>7024438</v>
+        <v>7024449</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,45 +3585,61 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129351711</v>
+        <v>129351705</v>
       </c>
       <c r="B32" t="n">
-        <v>92046</v>
+        <v>58114</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Pållbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503762</v>
+        <v>503874</v>
       </c>
       <c r="R32" t="n">
-        <v>7024433</v>
+        <v>7024459</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,32 +3698,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129351707</v>
+        <v>129351690</v>
       </c>
       <c r="B33" t="n">
-        <v>92548</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503860</v>
+        <v>503573</v>
       </c>
       <c r="R33" t="n">
-        <v>7024455</v>
+        <v>7024465</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,32 +3795,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129351697</v>
+        <v>129351719</v>
       </c>
       <c r="B34" t="n">
-        <v>91557</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3830,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503903</v>
+        <v>503825</v>
       </c>
       <c r="R34" t="n">
-        <v>7024440</v>
+        <v>7024437</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3897,32 +3892,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129351695</v>
+        <v>129351720</v>
       </c>
       <c r="B35" t="n">
-        <v>83050</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3932,10 +3927,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503792</v>
+        <v>503889</v>
       </c>
       <c r="R35" t="n">
-        <v>7024449</v>
+        <v>7024460</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3968,6 +3963,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>14st bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3994,32 +3994,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129351712</v>
+        <v>129351717</v>
       </c>
       <c r="B36" t="n">
-        <v>92046</v>
+        <v>78339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>228579</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503774</v>
+        <v>503809</v>
       </c>
       <c r="R36" t="n">
-        <v>7024452</v>
+        <v>7024430</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4091,10 +4091,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129351696</v>
+        <v>129351718</v>
       </c>
       <c r="B37" t="n">
-        <v>97020</v>
+        <v>78339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4102,21 +4102,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503909</v>
+        <v>503792</v>
       </c>
       <c r="R37" t="n">
-        <v>7024442</v>
+        <v>7024449</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 44532-2025 artfynd.xlsx
+++ b/artfynd/A 44532-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351696</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351713</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351714</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351715</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351716</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351721</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351723</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351698</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351699</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351700</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351701</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351710</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351711</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351712</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351702</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351703</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351689</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351706</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351707</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351708</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351709</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351697</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351691</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351724</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351725</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351726</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351692</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351693</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351694</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351695</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3695,6 +3850,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351705</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3792,6 +3952,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351690</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3889,6 +4054,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351719</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3991,6 +4161,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351720</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4088,6 +4263,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351717</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4185,8 +4365,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129351718</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>